--- a/dados/SURVEY_CBO_D2.xlsx
+++ b/dados/SURVEY_CBO_D2.xlsx
@@ -552,7 +552,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,7 +648,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -1600,7 +1600,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>under using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -2652,7 +2652,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>restricted manoeuvrability</t>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>restricted manoeuvrability</t>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>restricted manoeuvrability</t>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -3704,7 +3704,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -4740,7 +4740,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -4836,7 +4836,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -5788,7 +5788,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -6840,7 +6840,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -8896,7 +8896,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At anchor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -9944,7 +9944,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -10996,7 +10996,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>restricted manoeuvrability</t>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>restricted manoeuvrability</t>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>restricted manoeuvrability</t>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -12048,7 +12048,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -13104,7 +13104,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Underway using Engin</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -14156,7 +14156,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -15208,7 +15208,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -16260,7 +16260,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -16418,7 +16418,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -16650,7 +16650,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -18008,7 +18008,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -18054,7 +18054,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -18112,7 +18112,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -18170,7 +18170,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stooped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -18344,7 +18344,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -18402,7 +18402,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -18460,7 +18460,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -18518,7 +18518,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -18576,7 +18576,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -18750,7 +18750,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -18808,7 +18808,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -19040,7 +19040,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -19156,7 +19156,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -19330,7 +19330,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -19388,7 +19388,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -19446,7 +19446,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -20460,7 +20460,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -20502,7 +20502,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -20556,7 +20556,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -21508,7 +21508,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>resctricted manoeuvrability</t>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -21550,7 +21550,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>under using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -21604,7 +21604,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -23728,7 +23728,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -23770,7 +23770,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -23886,7 +23886,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -24838,7 +24838,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -24938,7 +24938,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K4" t="n">

--- a/dados/SURVEY_CBO_D2.xlsx
+++ b/dados/SURVEY_CBO_D2.xlsx
@@ -10614,21 +10614,21 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>35.904</v>
+        <v>33.003</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>FPSO CIDADE CAMPOSDOS GOYTACAZES</t>
+          <t>PETROBRAS 65 (P-65)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>tartaruga verde</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O15" t="n">

--- a/dados/SURVEY_CBO_D2.xlsx
+++ b/dados/SURVEY_CBO_D2.xlsx
@@ -14652,21 +14652,21 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>53.248</v>
+        <v>51.648</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>NS 54 (VALARIS DS 4)</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>navio sonda</t>
+          <t>FPSO</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>exploração desconhecida</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -14826,21 +14826,21 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>95.33499999999999</v>
+        <v>82.87</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>NS 54 (VALARIS DS 4)</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>navio sonda</t>
+          <t>FPSO</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>exploração desconhecida</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -15116,21 +15116,21 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>52.479</v>
+        <v>52.444</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>NS 54 (VALARIS DS 4)</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>navio sonda</t>
+          <t>FPSO</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>exploração desconhecida</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -15174,21 +15174,21 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>52.597</v>
+        <v>52.316</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>NS 54 (VALARIS DS 4)</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>navio sonda</t>
+          <t>FPSO</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>exploração desconhecida</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -15232,21 +15232,21 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>52.654</v>
+        <v>52.272</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>NS 54 (VALARIS DS 4)</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>navio sonda</t>
+          <t>FPSO</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>exploração desconhecida</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -15290,21 +15290,21 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>52.654</v>
+        <v>52.272</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>NS 54 (VALARIS DS 4)</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>navio sonda</t>
+          <t>FPSO</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>exploração desconhecida</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -26262,11 +26262,11 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>29.581</v>
+        <v>2.775</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -26276,11 +26276,11 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
@@ -26320,11 +26320,11 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>45.365</v>
+        <v>22.117</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -26378,11 +26378,11 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>29.536</v>
+        <v>1.698</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -26392,11 +26392,11 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.02361111111111111</v>
@@ -26436,11 +26436,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>28.543</v>
+        <v>3.061</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -26450,11 +26450,11 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.0125</v>
@@ -26494,11 +26494,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>29.439</v>
+        <v>2.309</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -26508,11 +26508,11 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.003472164351851852</v>
@@ -26552,11 +26552,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>30.091</v>
+        <v>1.161</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -26566,11 +26566,11 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.004861111111111111</v>
@@ -26610,11 +26610,11 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>29.79</v>
+        <v>1.466</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -26624,11 +26624,11 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.1777777777777778</v>
@@ -26668,11 +26668,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>29.79</v>
+        <v>1.466</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -26682,11 +26682,11 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.7263888888888889</v>
@@ -26726,11 +26726,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>29.79</v>
+        <v>1.466</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -26740,11 +26740,11 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>1.103472222222222</v>
@@ -26784,11 +26784,11 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>30.087</v>
+        <v>1.788</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -26798,11 +26798,11 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>0.5847222222222223</v>
@@ -26842,11 +26842,11 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>30.087</v>
+        <v>1.788</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -26856,11 +26856,11 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.9680555555555556</v>
@@ -26900,11 +26900,11 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>30.087</v>
+        <v>1.788</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -26914,11 +26914,11 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.084027719907407</v>
@@ -26958,11 +26958,11 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>28.242</v>
+        <v>3.454</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -26972,11 +26972,11 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.325</v>
@@ -27016,11 +27016,11 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>28.229</v>
+        <v>3.095</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -27030,11 +27030,11 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.002083333333333333</v>
@@ -27074,11 +27074,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>28.155</v>
+        <v>3.118</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -27088,11 +27088,11 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.00625</v>
@@ -27132,11 +27132,11 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>29.764</v>
+        <v>2.845</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -27146,11 +27146,11 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.001388888888888889</v>
@@ -27190,11 +27190,11 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>30.501</v>
+        <v>1.223</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CIDADE ILHA BELA</t>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -27204,11 +27204,11 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>sapinhoá</t>
+          <t>lapa</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0.01041666666666667</v>

--- a/dados/SURVEY_CBO_D2.xlsx
+++ b/dados/SURVEY_CBO_D2.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1602,6 +1602,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>1.393055555555555</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.359722222222222</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46234.65347222222</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3.747222222222222</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.63333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>89.93333333333334</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1.243</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.005555555555555556</v>
       </c>
     </row>
   </sheetData>
@@ -1615,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2770,6 +2828,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.359722222222222</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46232.79652777778</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.4993055555555556</v>
+      </c>
+      <c r="E21" t="n">
+        <v>110.07</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.63333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>11.98333333333333</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>78.319</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PEREGRINO C</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Fixa (Habitada)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>peregrino</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>1.8625</v>
       </c>
     </row>
   </sheetData>
@@ -2783,7 +2899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3938,6 +4054,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.001388888888888889</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.360416666666667</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46234.65972222222</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.359027777777778</v>
+      </c>
+      <c r="E21" t="n">
+        <v>94.06999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>56.61666666666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.002777777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -3951,7 +4125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5102,6 +5276,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.360416666666667</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46234.65833333333</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.358333333333333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>242.61</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1.244</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.004166666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -5115,7 +5347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6266,6 +6498,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.360416666666667</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46232.60555555556</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7.333333333333333</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>29.284</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PETROBRAS 68 (P-68)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>berbigao</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.056944444444444</v>
       </c>
     </row>
   </sheetData>
@@ -6279,7 +6569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7434,6 +7724,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.002777777777777778</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.360416666666667</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.359722222222222</v>
+      </c>
+      <c r="E21" t="n">
+        <v>267.83</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>56.63333333333333</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.003472222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -7447,7 +7795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8590,6 +8938,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.3465277777777778</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.360416666666667</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46233.62013888889</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1.664583333333333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>24.124</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>FPSO FRADE</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>frade</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>1.042361111111111</v>
       </c>
     </row>
   </sheetData>
@@ -8603,7 +9009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9758,6 +10164,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>1554.490972222222</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.360416666666667</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>44677.81111111111</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>637.95</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NS 54 (VALARIS DS 4)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>exploração desconhecida</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>1556.851388888889</v>
       </c>
     </row>
   </sheetData>
@@ -9771,7 +10235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10926,6 +11390,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.360416666666667</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46233.05416666667</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E21" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6.364</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>FPSO PEREGRINO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>peregrino</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>1.608333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -10939,7 +11461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12094,6 +12616,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>392.7256944444445</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.360416666666667</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>45839.57638888889</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1.947</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BR NTR</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>porto niteroi</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>395.0861111111111</v>
       </c>
     </row>
   </sheetData>
@@ -12107,7 +12687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13262,6 +13842,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.001388888888888889</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.360416666666667</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46232.63888888889</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.3381944444444445</v>
+      </c>
+      <c r="E21" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8.116666666666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>3.931</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>FPSO SEPETIBA</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>mero</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.023611111111111</v>
       </c>
     </row>
   </sheetData>
@@ -13275,7 +13913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14434,6 +15072,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.003472222222222222</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.359722222222222</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46232.57638888889</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.2805555555555556</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.63333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6.733333333333333</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PETROBRAS 69 (P-69)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>tupi</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.082638888888889</v>
       </c>
     </row>
   </sheetData>
@@ -14447,7 +15143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15602,6 +16298,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.360416666666667</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46233.68263888889</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1.382638888888889</v>
+      </c>
+      <c r="E21" t="n">
+        <v>302.26</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>33.18333333333333</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>51.99</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NS 54 (VALARIS DS 4)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>exploração desconhecida</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.9798611111111111</v>
       </c>
     </row>
   </sheetData>
@@ -15615,7 +16369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16770,6 +17524,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.65277777778</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.348611111111111</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46234.64791666667</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.345833333333333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.36666666666667</v>
+      </c>
+      <c r="G21" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.004861111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -16783,7 +17595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17938,6 +18750,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.01041666666666667</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.65277777778</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.348611111111111</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46234.64722222222</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.353472222222222</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.36666666666667</v>
+      </c>
+      <c r="G21" t="n">
+        <v>56.48333333333333</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.005555555555555556</v>
       </c>
     </row>
   </sheetData>
@@ -17951,7 +18821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19802,6 +20672,64 @@
       </c>
       <c r="P32" s="3" t="n">
         <v>0.002777777777777778</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>2.359722222222222</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>46234.21458333333</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1.918055555555556</v>
+      </c>
+      <c r="E33" t="n">
+        <v>135.86</v>
+      </c>
+      <c r="F33" t="n">
+        <v>56.63333333333333</v>
+      </c>
+      <c r="G33" t="n">
+        <v>46.03333333333333</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>83.402</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>0.4444444444444444</v>
       </c>
     </row>
   </sheetData>
@@ -19815,7 +20743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22370,6 +23298,64 @@
       </c>
       <c r="P44" s="3" t="n">
         <v>0.1770833333333333</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>2.359722222222222</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>46234.65069444444</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>2.528472222222222</v>
+      </c>
+      <c r="E45" t="n">
+        <v>205.44</v>
+      </c>
+      <c r="F45" t="n">
+        <v>56.63333333333333</v>
+      </c>
+      <c r="G45" t="n">
+        <v>60.68333333333333</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>0.008333333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -22383,7 +23369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23534,6 +24520,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>1841.734027777778</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.359722222222222</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>44390.56527777778</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.63333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>2.043</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BR NTR</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>porto niteroi</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>1844.09375</v>
       </c>
     </row>
   </sheetData>
@@ -23547,7 +24591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24698,6 +25742,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.004861111111111111</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.359722222222222</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46234.65277777778</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.358333333333333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>217.67</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.63333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.00625</v>
       </c>
     </row>
   </sheetData>
@@ -24711,7 +25813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25986,6 +27088,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.01041666666666667</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>2.359722222222222</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2.36875</v>
+      </c>
+      <c r="E23" t="n">
+        <v>150.84</v>
+      </c>
+      <c r="F23" t="n">
+        <v>56.63333333333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>45.141</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.001388888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -25999,7 +27159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27212,6 +28372,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.01041666666666667</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>2.359722222222222</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2.36875</v>
+      </c>
+      <c r="E22" t="n">
+        <v>295.41</v>
+      </c>
+      <c r="F22" t="n">
+        <v>56.63333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>2.747</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Rio</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Rio</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.001388888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -27225,7 +28443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28362,6 +29580,60 @@
         <v>0.2597222222222222</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.359722222222222</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46234.64305555556</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.603472222222222</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.63333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>62.48333333333333</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>3.834</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PETROBRAS 55 (P-55)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Produção</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.01597222222222222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados/SURVEY_CBO_D2.xlsx
+++ b/dados/SURVEY_CBO_D2.xlsx
@@ -5780,11 +5780,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>25.179</v>
+        <v>1.983</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PETROBRAS 69 (P-69)</t>
+          <t>FPSO CIDADE MARICA</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.005555555555555556</v>
@@ -5838,11 +5838,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>25.29</v>
+        <v>1.88</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PETROBRAS 69 (P-69)</t>
+          <t>FPSO CIDADE MARICA</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -5856,7 +5856,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.03125</v>
@@ -5896,11 +5896,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>28.524</v>
+        <v>1.161</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -5910,11 +5910,11 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.08819444444444445</v>
@@ -5954,11 +5954,11 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>28.524</v>
+        <v>1.161</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5968,11 +5968,11 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.6423611111111112</v>
@@ -6012,11 +6012,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>28.524</v>
+        <v>1.161</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -6026,11 +6026,11 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.033333333333333</v>
@@ -6070,11 +6070,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>28.524</v>
+        <v>1.161</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6084,11 +6084,11 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>1.641666666666667</v>
@@ -6128,11 +6128,11 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>25.265</v>
+        <v>1.864</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PETROBRAS 69 (P-69)</t>
+          <t>FPSO CIDADE MARICA</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6146,7 +6146,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>0.03680555555555556</v>
@@ -6186,11 +6186,11 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>25.265</v>
+        <v>1.864</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PETROBRAS 69 (P-69)</t>
+          <t>FPSO CIDADE MARICA</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6204,7 +6204,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>1.158333333333333</v>
@@ -6360,11 +6360,11 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>28.529</v>
+        <v>1.153</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -6374,11 +6374,11 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.02222222222222222</v>
@@ -6418,11 +6418,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>28.592</v>
+        <v>1.11</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -6432,11 +6432,11 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.002777777777777778</v>
@@ -6476,11 +6476,11 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>29.272</v>
+        <v>0.157</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -6490,11 +6490,11 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.002083333333333333</v>
@@ -6534,11 +6534,11 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>29.284</v>
+        <v>0.147</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -6548,11 +6548,11 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>2.056944444444444</v>
@@ -6716,11 +6716,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>26.223</v>
+        <v>3.757</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -6730,11 +6730,11 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P3" s="3" t="n">
         <v>1.481944444444445</v>
@@ -6774,11 +6774,11 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>26.223</v>
+        <v>3.757</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -6788,11 +6788,11 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>1.847222222222222</v>
@@ -6832,11 +6832,11 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>24.594</v>
+        <v>5.402</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -6846,11 +6846,11 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0.7590277777777777</v>
@@ -7064,11 +7064,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>24.62</v>
+        <v>5.382</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -7078,11 +7078,11 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.08888888888888889</v>
@@ -7122,11 +7122,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>24.642</v>
+        <v>5.373</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -7136,11 +7136,11 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.08819444444444445</v>
@@ -7180,11 +7180,11 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>24.642</v>
+        <v>5.373</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -7194,11 +7194,11 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.6423611111111112</v>
@@ -7238,11 +7238,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>24.642</v>
+        <v>5.373</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -7252,11 +7252,11 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.033333333333333</v>
@@ -7296,11 +7296,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>24.642</v>
+        <v>5.373</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -7310,11 +7310,11 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>1.641666666666667</v>
@@ -7354,11 +7354,11 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>24.642</v>
+        <v>5.373</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE MANGARATIBA</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -7368,11 +7368,11 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>2.021527777777778</v>
@@ -14818,11 +14818,11 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>7.076</v>
+        <v>0.195</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PETROBRAS 69 (P-69)</t>
+          <t>PETROBRAS 66 (P-66)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -14836,7 +14836,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>0.025</v>
@@ -14876,11 +14876,11 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>7.037</v>
+        <v>0.24</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PETROBRAS 69 (P-69)</t>
+          <t>PETROBRAS 66 (P-66)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -14894,7 +14894,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.16875</v>
@@ -14934,11 +14934,11 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>4.19</v>
+        <v>3.079</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PETROBRAS 69 (P-69)</t>
+          <t>PETROBRAS 66 (P-66)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -14992,11 +14992,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6.797</v>
+        <v>3.373</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>PETROBRAS 69 (P-69)</t>
+          <t>PETROBRAS 66 (P-66)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -15010,7 +15010,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.001388888888888889</v>
@@ -15050,11 +15050,11 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>5.618</v>
+        <v>2.394</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PETROBRAS 69 (P-69)</t>
+          <t>PETROBRAS 66 (P-66)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -15068,7 +15068,7 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.003472222222222222</v>
@@ -15108,11 +15108,11 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>4.74</v>
+        <v>2.722</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>PETROBRAS 69 (P-69)</t>
+          <t>PETROBRAS 66 (P-66)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -15126,7 +15126,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>2.082638888888889</v>
@@ -27364,11 +27364,11 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>68.593</v>
+        <v>53.426</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PETROBRAS 71 (P-71)</t>
+          <t>FPSO CIDADE ITAGUAI</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -27378,7 +27378,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>itapu</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O4" t="n">

--- a/dados/SURVEY_CBO_D2.xlsx
+++ b/dados/SURVEY_CBO_D2.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1660,6 +1660,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.005555555555555556</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7486111111111111</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.7520833333333333</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17.96666666666667</v>
+      </c>
+      <c r="G22" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.002083333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1673,7 +1731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2886,6 +2944,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>1.8625</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7486111111111111</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46235.11458333334</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2.318055555555556</v>
+      </c>
+      <c r="E22" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17.96666666666667</v>
+      </c>
+      <c r="G22" t="n">
+        <v>55.63333333333333</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>6.612</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>LONE STAR</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>papa-terra</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.2930555555555556</v>
       </c>
     </row>
   </sheetData>
@@ -2899,7 +3015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3452,11 +3568,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>24.097</v>
+        <v>5.728</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>PETROBRAS 70 (P-70)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -3466,11 +3582,11 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.3097222222222222</v>
@@ -3510,11 +3626,11 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>24.097</v>
+        <v>5.728</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>PETROBRAS 70 (P-70)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -3524,11 +3640,11 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.8638888888888889</v>
@@ -3568,11 +3684,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>24.097</v>
+        <v>5.728</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>PETROBRAS 70 (P-70)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -3582,11 +3698,11 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.254861111111111</v>
@@ -3626,11 +3742,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>24.097</v>
+        <v>5.728</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>PETROBRAS 70 (P-70)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -3640,11 +3756,11 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>1.863194444444444</v>
@@ -3684,11 +3800,11 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>24.097</v>
+        <v>5.728</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>PETROBRAS 70 (P-70)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -3698,11 +3814,11 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>2.243055555555555</v>
@@ -3858,11 +3974,11 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>24.999</v>
+        <v>6.877</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>PETROBRAS 70 (P-70)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -3872,11 +3988,11 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.1222222222222222</v>
@@ -4112,6 +4228,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.002777777777777778</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46235.41319444445</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.7534722222222222</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18.13333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>18.08333333333333</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.004861111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -4125,7 +4299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5334,6 +5508,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.004166666666666667</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46235.41666666666</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.7583333333333333</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18.13333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.001388888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -5347,7 +5579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6244,11 +6476,11 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>19.005</v>
+        <v>5.131</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>P-75_FSO</t>
+          <t>PETROBRAS 70 (P-70)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -6258,11 +6490,11 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>buzios</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>0.1958333333333333</v>
@@ -6556,6 +6788,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>2.056944444444444</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46232.60555555556</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18.13333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>FPSO CIDADE MANGARATIBA</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>tupi</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>2.8125</v>
       </c>
     </row>
   </sheetData>
@@ -6569,7 +6859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6948,11 +7238,11 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>18.536</v>
+        <v>3.252</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>PETROBRAS 70 (P-70)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -6962,11 +7252,11 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.01388888888888889</v>
@@ -7006,11 +7296,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>17.8</v>
+        <v>3.838</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>PETROBRAS 70 (P-70)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -7020,11 +7310,11 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.005555555555555556</v>
@@ -7644,11 +7934,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>19.356</v>
+        <v>0.113</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>P-75_FSO</t>
+          <t>PETROBRAS 70 (P-70)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -7658,11 +7948,11 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>buzios</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.002083333333333333</v>
@@ -7782,6 +8072,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.003472222222222222</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46235.41666666666</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.7576388888888889</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18.13333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>18.18333333333333</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.001388888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -7795,7 +8143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8996,6 +9344,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>1.042361111111111</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46234.74513888889</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="E22" t="n">
+        <v>69.06999999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18.13333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>27</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>P 58</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>jubarte</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.6729166666666667</v>
       </c>
     </row>
   </sheetData>
@@ -9009,7 +9415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10222,6 +10628,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>1556.851388888889</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>44677.81111111111</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18.13333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>637.95</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NS 54 (VALARIS DS 4)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>exploração desconhecida</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>1557.606944444444</v>
       </c>
     </row>
   </sheetData>
@@ -10235,7 +10699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11448,6 +11912,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>1.608333333333333</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46235.17986111111</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2.125694444444445</v>
+      </c>
+      <c r="E22" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18.13333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>51.01666666666667</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PEREGRINO C</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Fixa (Habitada)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>peregrino</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.2381944444444444</v>
       </c>
     </row>
   </sheetData>
@@ -11461,7 +11983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12674,6 +13196,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>395.0861111111111</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>45839.57638888889</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18.13333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1.947</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BR NTR</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>porto niteroi</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>395.8416666666666</v>
       </c>
     </row>
   </sheetData>
@@ -12687,7 +13267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13900,6 +14480,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>2.023611111111111</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46232.63888888889</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18.13333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>3.931</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>FPSO SEPETIBA</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>mero</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>2.779166666666667</v>
       </c>
     </row>
   </sheetData>
@@ -13913,7 +14551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15130,6 +15768,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>2.082638888888889</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7486111111111111</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46232.57638888889</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17.96666666666667</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PETROBRAS 66 (P-66)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>tupi</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>2.83125</v>
       </c>
     </row>
   </sheetData>
@@ -15143,7 +15839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16356,6 +17052,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.9798611111111111</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46233.68263888889</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18.13333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>51.99</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NS 54 (VALARIS DS 4)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>exploração desconhecida</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>1.735416666666667</v>
       </c>
     </row>
   </sheetData>
@@ -16369,7 +17123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17582,6 +18336,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.004861111111111111</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.42013888889</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7673611111111112</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46235.41666666666</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.76875</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18.41666666666667</v>
+      </c>
+      <c r="G22" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.003472222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -17595,7 +18407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18808,6 +19620,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.005555555555555556</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.42013888889</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7673611111111112</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.7708333333333334</v>
+      </c>
+      <c r="E22" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18.41666666666667</v>
+      </c>
+      <c r="G22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Underway</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>15.814</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.002083333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -18821,7 +19691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20730,6 +21600,64 @@
       </c>
       <c r="P33" s="3" t="n">
         <v>0.4444444444444444</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>0.7486111111111111</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>46235.08680555555</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0.8722222222222222</v>
+      </c>
+      <c r="E34" t="n">
+        <v>138.7</v>
+      </c>
+      <c r="F34" t="n">
+        <v>17.96666666666667</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20.93333333333333</v>
+      </c>
+      <c r="H34" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>3R-3 (Ex-PETROBRAS 63)</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>papa-terra</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>0.3208333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -20743,7 +21671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23356,6 +24284,64 @@
       </c>
       <c r="P45" s="3" t="n">
         <v>0.008333333333333333</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>0.7486111111111111</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>46235.40486111111</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>17.96666666666667</v>
+      </c>
+      <c r="G46" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>0.002777777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -23369,7 +24355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24578,6 +25564,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>1844.09375</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7486111111111111</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>44390.56527777778</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17.96666666666667</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>2.043</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BR NTR</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>porto niteroi</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>1844.842361111111</v>
       </c>
     </row>
   </sheetData>
@@ -24591,7 +25635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25800,6 +26844,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.00625</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7486111111111111</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46235.39444444444</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="E22" t="n">
+        <v>66.56999999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17.96666666666667</v>
+      </c>
+      <c r="G22" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>62.494</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.01319444444444444</v>
       </c>
     </row>
   </sheetData>
@@ -25813,7 +26915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27146,6 +28248,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.001388888888888889</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.7486111111111111</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46235.40486111111</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.7472222222222222</v>
+      </c>
+      <c r="E24" t="n">
+        <v>47.49</v>
+      </c>
+      <c r="F24" t="n">
+        <v>17.96666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>17.93333333333333</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.002777777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -27159,7 +28319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28430,6 +29590,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.001388888888888889</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.7486111111111111</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46235.06111111111</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.4034722222222222</v>
+      </c>
+      <c r="E23" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="F23" t="n">
+        <v>17.96666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9.683333333333334</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>47.779</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.3465277777777778</v>
       </c>
     </row>
   </sheetData>
@@ -28443,7 +29661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28570,7 +29788,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>8215.690000000001</v>
+        <v>129.51</v>
       </c>
       <c r="F3" t="n">
         <v>48</v>
@@ -28579,10 +29797,10 @@
         <v>48</v>
       </c>
       <c r="H3" t="n">
-        <v>171.16</v>
+        <v>2.7</v>
       </c>
       <c r="I3" t="n">
-        <v>92.42</v>
+        <v>1.46</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -28864,23 +30082,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2.995</v>
+        <v>1.226</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>LAGUNA STAR (NS44)</t>
+          <t>NORBE VIII (NS 32)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>navio sonda</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>roncador</t>
-        </is>
-      </c>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
         <v>0.8</v>
       </c>
@@ -28922,25 +30136,21 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.78</v>
+        <v>1.301</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>LAGUNA STAR (NS44)</t>
+          <t>NORBE VIII (NS 32)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>navio sonda</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>roncador</t>
-        </is>
-      </c>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.1180555555555556</v>
@@ -29556,25 +30766,21 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3.133</v>
+        <v>1.593</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>LAGUNA STAR (NS44)</t>
+          <t>NORBE VIII (NS 32)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>navio sonda</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>roncador</t>
-        </is>
-      </c>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.2597222222222222</v>
@@ -29632,6 +30838,60 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.01597222222222222</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7486111111111111</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46235.17708333334</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.5340277777777778</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17.96666666666667</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12.81666666666667</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>3.929</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PETROBRAS 55 (P-55)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Produção</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.2305555555555556</v>
       </c>
     </row>
   </sheetData>

--- a/dados/SURVEY_CBO_D2.xlsx
+++ b/dados/SURVEY_CBO_D2.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1718,6 +1718,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35555555556</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.35416666666</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9486111111111111</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22.76666666666667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1.218</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.001388888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -1731,7 +1789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3002,6 +3060,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2930555555555556</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35555555556</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.23125</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1.116666666666667</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>9.106999999999999</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>LONE STAR</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>papa-terra</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.1243055555555556</v>
       </c>
     </row>
   </sheetData>
@@ -3015,7 +3131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4286,6 +4402,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.004861111111111111</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35902777778</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9409722222222222</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.35555555556</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9423611111111111</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22.61666666666667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1.268</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.003472222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -4299,7 +4473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5566,6 +5740,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.001388888888888889</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35902777778</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9409722222222222</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.35625</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9395833333333333</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.002777777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -5579,7 +5811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6846,6 +7078,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>2.8125</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35902777778</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9409722222222222</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.21944444445</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>3.613888888888889</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>86.73333333333333</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>9.196999999999999</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>FPSO CIDADE MANGARATIBA</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>tupi</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.1395833333333333</v>
       </c>
     </row>
   </sheetData>
@@ -6859,7 +7149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8129,6 +8419,64 @@
         <v>0.8</v>
       </c>
       <c r="P22" s="3" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35902777778</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9409722222222222</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.35763888889</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9409722222222222</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1.278</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
         <v>0.001388888888888889</v>
       </c>
     </row>
@@ -8143,7 +8491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9402,6 +9750,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.6729166666666667</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35902777778</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9409722222222222</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46234.74513888889</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>3.104</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PETROBRAS 57 (P-57)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>jubarte</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>1.613888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -9415,7 +9821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10686,6 +11092,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>1557.606944444444</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35902777778</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9409722222222222</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>44677.81111111111</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>637.95</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NS 54 (VALARIS DS 4)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>exploração desconhecida</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>1558.547916666667</v>
       </c>
     </row>
   </sheetData>
@@ -10699,7 +11163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11970,6 +12434,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2381944444444444</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35902777778</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9409722222222222</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.25208333333</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1.072222222222222</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>25.73333333333333</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>2.872</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PEREGRINO C</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Fixa (Habitada)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>peregrino</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.1069444444444444</v>
       </c>
     </row>
   </sheetData>
@@ -11983,7 +12505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13254,6 +13776,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>395.8416666666666</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35902777778</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9409722222222222</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>45839.57638888889</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1.947</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BR NTR</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>porto niteroi</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>396.7826388888889</v>
       </c>
     </row>
   </sheetData>
@@ -13267,7 +13847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14538,6 +15118,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>2.779166666666667</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35902777778</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9409722222222222</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.21736111111</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>3.578472222222222</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>85.88333333333334</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>3.903</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>FPSO SEPETIBA</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>mero</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.1416666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -14551,7 +15189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15826,6 +16464,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>2.83125</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35555555556</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46235.79236111111</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>3.215972222222222</v>
+      </c>
+      <c r="E23" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>77.18333333333334</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>3.468</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PETROBRAS 67 (P-67)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>tupi</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.5631944444444444</v>
       </c>
     </row>
   </sheetData>
@@ -15839,7 +16535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17110,6 +17806,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>1.735416666666667</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35902777778</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9409722222222222</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.12916666667</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2.446527777777778</v>
+      </c>
+      <c r="E23" t="n">
+        <v>109.64</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>58.71666666666667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>58.203</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>FPSO CIDADE ITAGUAI</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>tupi</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.2298611111111111</v>
       </c>
     </row>
   </sheetData>
@@ -17123,7 +17877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18394,6 +19148,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.003472222222222222</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.34930555556</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9291666666666667</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.34375</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9270833333333334</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.005555555555555556</v>
       </c>
     </row>
   </sheetData>
@@ -18407,7 +19219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19678,6 +20490,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.34930555556</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9291666666666667</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.34652777778</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9284722222222223</v>
+      </c>
+      <c r="E23" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22.28333333333333</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.002777777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -19691,7 +20561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21658,6 +22528,64 @@
       </c>
       <c r="P34" s="3" t="n">
         <v>0.3208333333333334</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46236.35555555556</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>46236.18194444444</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1.095138888888889</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G35" t="n">
+        <v>26.28333333333333</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>6.655</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>LONE STAR</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>papa-terra</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>0.1736111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -21671,7 +22599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24342,6 +25270,64 @@
       </c>
       <c r="P46" s="3" t="n">
         <v>0.002777777777777778</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46236.35555555556</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>46235.93611111111</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="E47" t="n">
+        <v>90.09</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G47" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>90.032</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>0.4194444444444445</v>
       </c>
     </row>
   </sheetData>
@@ -24355,7 +25341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25622,6 +26608,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>1844.842361111111</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35555555556</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>44390.56527777778</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>2.043</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BR NTR</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>porto niteroi</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>1845.790277777778</v>
       </c>
     </row>
   </sheetData>
@@ -25635,7 +26679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26902,6 +27946,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.01319444444444444</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35555555556</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.34583333333</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9513888888888888</v>
+      </c>
+      <c r="E23" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>93.23399999999999</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.009722222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -26915,7 +28017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28306,6 +29408,64 @@
       </c>
       <c r="P24" s="3" t="n">
         <v>0.002777777777777778</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46236.35555555556</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>46236.35347222222</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0.9486111111111111</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="F25" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G25" t="n">
+        <v>22.76666666666667</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0.002083333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -28319,7 +29479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29648,6 +30808,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.3465277777777778</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46236.35555555556</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46236.18125</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1.120138888888889</v>
+      </c>
+      <c r="E24" t="n">
+        <v>248.56</v>
+      </c>
+      <c r="F24" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G24" t="n">
+        <v>26.88333333333333</v>
+      </c>
+      <c r="H24" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>2.603</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>lapa</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.1743055555555555</v>
       </c>
     </row>
   </sheetData>
@@ -29661,7 +30879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30894,6 +32112,60 @@
         <v>0.2305555555555556</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35555555556</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.25833333333</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1.08125</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>3.729</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PETROBRAS 55 (P-55)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Produção</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.09722222222222222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados/SURVEY_CBO_D2.xlsx
+++ b/dados/SURVEY_CBO_D2.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1775,6 +1775,64 @@
         <v>0.8</v>
       </c>
       <c r="P23" s="3" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9736111111111111</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.32777777778</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.9736111111111111</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.36666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>23.36666666666667</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P24" s="3" t="n">
         <v>0.001388888888888889</v>
       </c>
     </row>
@@ -1789,7 +1847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3118,6 +3176,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.1243055555555556</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9736111111111111</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.15555555555</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.9243055555555556</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.36666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>22.18333333333333</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>LONE STAR</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>papa-terra</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.1736111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -3131,7 +3247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4460,6 +4576,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.003472222222222222</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9715277777777778</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.32083333333</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.9652777777777778</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.31666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>23.16666666666667</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.009722222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -4473,7 +4647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5798,6 +5972,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.002777777777777778</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9715277777777778</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.32083333333</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.9645833333333333</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.31666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.009722222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -5811,7 +6043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7136,6 +7368,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.1395833333333333</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9715277777777778</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.32708333333</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1.107638888888889</v>
+      </c>
+      <c r="E24" t="n">
+        <v>255.53</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.31666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>26.58333333333333</v>
+      </c>
+      <c r="H24" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.003472222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -7149,7 +7439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8478,6 +8768,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.001388888888888889</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9715277777777778</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.32430555556</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.31666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.00625</v>
       </c>
     </row>
   </sheetData>
@@ -8491,7 +8839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9808,6 +10156,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>1.613888888888889</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9715277777777778</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46234.74513888889</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.31666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>3.104</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>PETROBRAS 57 (P-57)</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>jubarte</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>2.585416666666667</v>
       </c>
     </row>
   </sheetData>
@@ -9821,7 +10227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11150,6 +11556,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>1558.547916666667</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9715277777777778</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>44677.81111111111</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.31666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>637.95</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NS 54 (VALARIS DS 4)</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>exploração desconhecida</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>1559.519444444444</v>
       </c>
     </row>
   </sheetData>
@@ -11163,7 +11627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12492,6 +12956,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.1069444444444444</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9715277777777778</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.32777777778</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1.075694444444445</v>
+      </c>
+      <c r="E24" t="n">
+        <v>113.51</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.31666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>25.81666666666667</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>38.333</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>PETROBRAS 65 (P-65)</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Produção</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>marimbá</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.002777777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -12505,7 +13027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13834,6 +14356,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>396.7826388888889</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9715277777777778</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>45839.57638888889</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.31666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1.947</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>BR NTR</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>porto niteroi</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>397.7541666666667</v>
       </c>
     </row>
   </sheetData>
@@ -13847,7 +14427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15176,6 +15756,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.1416666666666667</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9715277777777778</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.03888888889</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.8215277777777777</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.31666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>19.71666666666667</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>3.958</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>FPSO SEPETIBA</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>mero</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.2916666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -15189,7 +15827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16522,6 +17160,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.5631944444444444</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9736111111111111</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.32777777778</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1.535416666666667</v>
+      </c>
+      <c r="E24" t="n">
+        <v>340.33</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.36666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="H24" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Porto de imbetiba</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>porto macae</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.001388888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -16535,7 +17231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17864,6 +18560,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.2298611111111111</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9715277777777778</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.32708333333</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1.197916666666667</v>
+      </c>
+      <c r="E24" t="n">
+        <v>396.32</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.31666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="H24" t="n">
+        <v>17</v>
+      </c>
+      <c r="I24" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>BR ACX</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>porto açu</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.003472222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -17877,7 +18631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19206,6 +19960,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.005555555555555556</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.98125</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.32152777778</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.9777777777777777</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="G24" t="n">
+        <v>23.46666666666667</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.009027777777777777</v>
       </c>
     </row>
   </sheetData>
@@ -19219,7 +20031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20548,6 +21360,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.002777777777777778</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.98125</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.32152777778</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="G24" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.009027777777777777</v>
       </c>
     </row>
   </sheetData>
@@ -20561,7 +21431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22586,6 +23456,64 @@
       </c>
       <c r="P35" s="3" t="n">
         <v>0.1736111111111111</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>0.9736111111111111</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>46237.06319444445</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0.88125</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F36" t="n">
+        <v>23.36666666666667</v>
+      </c>
+      <c r="G36" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>6.149</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>LONE STAR</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>papa-terra</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>0.2659722222222222</v>
       </c>
     </row>
   </sheetData>
@@ -22599,7 +23527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25328,6 +26256,64 @@
       </c>
       <c r="P47" s="3" t="n">
         <v>0.4194444444444445</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>0.9736111111111111</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>46236.76388888889</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.8277777777777777</v>
+      </c>
+      <c r="E48" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="F48" t="n">
+        <v>23.36666666666667</v>
+      </c>
+      <c r="G48" t="n">
+        <v>19.86666666666667</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>2.034</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>PETROBRAS 74 (P-74)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>0.5652777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -25341,7 +26327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26666,6 +27652,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>1845.790277777778</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9736111111111111</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>44390.56527777778</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.36666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>2.043</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>BR NTR</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>porto niteroi</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>1846.763888888889</v>
       </c>
     </row>
   </sheetData>
@@ -26679,7 +27723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28004,6 +29048,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.009722222222222222</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9736111111111111</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.07291666666</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.7270833333333333</v>
+      </c>
+      <c r="E24" t="n">
+        <v>46.27</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.36666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>59.577</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>P-79</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.25625</v>
       </c>
     </row>
   </sheetData>
@@ -28017,7 +29119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29466,6 +30568,64 @@
       </c>
       <c r="P25" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0.9736111111111111</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>46237.32222222222</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="F26" t="n">
+        <v>23.36666666666667</v>
+      </c>
+      <c r="G26" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1.447</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>0.006944444444444444</v>
       </c>
     </row>
   </sheetData>
@@ -29479,7 +30639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30866,6 +32026,64 @@
       </c>
       <c r="P24" s="3" t="n">
         <v>0.1743055555555555</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>0.9736111111111111</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>46237.06319444445</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0.8819444444444444</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F25" t="n">
+        <v>23.36666666666667</v>
+      </c>
+      <c r="G25" t="n">
+        <v>21.16666666666667</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>3.106</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>FPSO CIDADE CARAGUATATUBA</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>lapa</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0.2659722222222222</v>
       </c>
     </row>
   </sheetData>
@@ -30879,7 +32097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32166,6 +33384,64 @@
         <v>0.09722222222222222</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9736111111111111</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.32430555556</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1.065972222222222</v>
+      </c>
+      <c r="E24" t="n">
+        <v>129.64</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.36666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>25.58333333333333</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>TechnipFMC Flexiveis</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>porto açu</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.004861111111111111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
